--- a/exports/trend_1d/POLICYBZR_full_report.xlsx
+++ b/exports/trend_1d/POLICYBZR_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:U37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>26.42</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44559</v>
+        <v>44560</v>
       </c>
       <c r="H2" t="n">
-        <v>961.45</v>
+        <v>929.05</v>
       </c>
       <c r="I2" t="n">
         <v>931.1874634999999</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K2" t="n">
-        <v>-20.91</v>
+        <v>-23.57</v>
       </c>
       <c r="L2" t="n">
         <v>27.2</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>20.07</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44575</v>
+        <v>44578</v>
       </c>
       <c r="H3" t="n">
-        <v>941.4</v>
+        <v>1022.6</v>
       </c>
       <c r="I3" t="n">
         <v>1010.225992174234</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.33</v>
+        <v>-10.07</v>
       </c>
       <c r="L3" t="n">
-        <v>4.63</v>
+        <v>13.34</v>
       </c>
       <c r="M3" t="n">
         <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>5.33</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="O3" t="n">
         <v>-3.37</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>17.84</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H4" t="n">
-        <v>864.25</v>
+        <v>777.15</v>
       </c>
       <c r="I4" t="n">
         <v>847.8347840344848</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>-15.49</v>
+        <v>-24</v>
       </c>
       <c r="L4" t="n">
-        <v>16.07</v>
+        <v>25.18</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04</v>
+        <v>0.62</v>
       </c>
       <c r="N4" t="n">
-        <v>6.96</v>
+        <v>10.08</v>
       </c>
       <c r="O4" t="n">
         <v>8.630000000000001</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>26.78</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44594</v>
+        <v>44595</v>
       </c>
       <c r="H5" t="n">
-        <v>900.8</v>
+        <v>936.5</v>
       </c>
       <c r="I5" t="n">
         <v>925.7353515379293</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>-15.91</v>
+        <v>-20.5</v>
       </c>
       <c r="L5" t="n">
-        <v>16.45</v>
+        <v>20.95</v>
       </c>
       <c r="M5" t="n">
         <v>1.71</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,25 +833,25 @@
         <v>23.03</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44603</v>
+        <v>44606</v>
       </c>
       <c r="H6" t="n">
-        <v>778.9</v>
+        <v>763.95</v>
       </c>
       <c r="I6" t="n">
         <v>767.9831260933313</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K6" t="n">
-        <v>-16.83</v>
+        <v>-18.42</v>
       </c>
       <c r="L6" t="n">
-        <v>17.31</v>
+        <v>19.91</v>
       </c>
       <c r="M6" t="n">
-        <v>3.24</v>
+        <v>3.71</v>
       </c>
       <c r="N6" t="n">
         <v>10.28</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>25.45</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44655</v>
+        <v>44656</v>
       </c>
       <c r="H7" t="n">
-        <v>766.9</v>
+        <v>816.2</v>
       </c>
       <c r="I7" t="n">
         <v>779.143609692195</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.39</v>
+        <v>-6.84</v>
       </c>
       <c r="L7" t="n">
-        <v>4.46</v>
+        <v>7.34</v>
       </c>
       <c r="M7" t="n">
         <v>2.3</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>17.19</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44677</v>
+        <v>44678</v>
       </c>
       <c r="H8" t="n">
-        <v>690.95</v>
+        <v>651</v>
       </c>
       <c r="I8" t="n">
         <v>675.8595858373333</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K8" t="n">
-        <v>-15.35</v>
+        <v>-20.24</v>
       </c>
       <c r="L8" t="n">
-        <v>15.58</v>
+        <v>20.49</v>
       </c>
       <c r="M8" t="n">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="N8" t="n">
         <v>6.69</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>20.35</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44694</v>
+        <v>44697</v>
       </c>
       <c r="H9" t="n">
-        <v>645.2</v>
+        <v>670.55</v>
       </c>
       <c r="I9" t="n">
         <v>668.9445675098358</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K9" t="n">
-        <v>0.89</v>
+        <v>-3</v>
       </c>
       <c r="L9" t="n">
-        <v>6.34</v>
+        <v>7.33</v>
       </c>
       <c r="M9" t="n">
         <v>4.79</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>23.83</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44750</v>
+        <v>44753</v>
       </c>
       <c r="H10" t="n">
-        <v>564.05</v>
+        <v>558.35</v>
       </c>
       <c r="I10" t="n">
         <v>563.6680973103237</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K10" t="n">
-        <v>-15.88</v>
+        <v>-16.73</v>
       </c>
       <c r="L10" t="n">
         <v>17.68</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>11.55</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44774</v>
+        <v>44775</v>
       </c>
       <c r="H11" t="n">
-        <v>504.2</v>
+        <v>559.4</v>
       </c>
       <c r="I11" t="n">
         <v>531.4082186748462</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K11" t="n">
-        <v>9.699999999999999</v>
+        <v>-0.19</v>
       </c>
       <c r="L11" t="n">
         <v>2.63</v>
@@ -1068,7 +1199,7 @@
         <v>1.43</v>
       </c>
       <c r="N11" t="n">
-        <v>7.68</v>
+        <v>10.95</v>
       </c>
       <c r="O11" t="n">
         <v>-1.01</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>19.21</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44805</v>
+        <v>44806</v>
       </c>
       <c r="H12" t="n">
-        <v>495.55</v>
+        <v>483.3</v>
       </c>
       <c r="I12" t="n">
         <v>492.7715060472191</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K12" t="n">
-        <v>-11.41</v>
+        <v>-13.6</v>
       </c>
       <c r="L12" t="n">
-        <v>12.14</v>
+        <v>13.92</v>
       </c>
       <c r="M12" t="n">
         <v>2.18</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>17.72</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44816</v>
+        <v>44817</v>
       </c>
       <c r="H13" t="n">
-        <v>505.05</v>
+        <v>565.05</v>
       </c>
       <c r="I13" t="n">
         <v>560.2360119062982</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.5</v>
+        <v>-16.91</v>
       </c>
       <c r="L13" t="n">
-        <v>7.92</v>
+        <v>18.97</v>
       </c>
       <c r="M13" t="n">
         <v>1.3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.95</v>
+        <v>11.88</v>
       </c>
       <c r="O13" t="n">
         <v>-2.47</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>18.46</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44832</v>
+        <v>44833</v>
       </c>
       <c r="H14" t="n">
-        <v>469.45</v>
+        <v>467.2</v>
       </c>
       <c r="I14" t="n">
         <v>469.05208282945</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K14" t="n">
-        <v>-16.92</v>
+        <v>-17.32</v>
       </c>
       <c r="L14" t="n">
         <v>18.41</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>15.26</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44888</v>
+        <v>44889</v>
       </c>
       <c r="H15" t="n">
-        <v>400.4</v>
+        <v>432</v>
       </c>
       <c r="I15" t="n">
         <v>428.6073374058853</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K15" t="n">
-        <v>14.3</v>
+        <v>7.53</v>
       </c>
       <c r="L15" t="n">
         <v>6.12</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>19.8</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44950</v>
+        <v>44951</v>
       </c>
       <c r="H16" t="n">
-        <v>420.65</v>
+        <v>405.95</v>
       </c>
       <c r="I16" t="n">
         <v>418.0810354135816</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.63</v>
+        <v>-6.03</v>
       </c>
       <c r="L16" t="n">
-        <v>7.41</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M16" t="n">
         <v>1.72</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>14.78</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44964</v>
+        <v>44965</v>
       </c>
       <c r="H17" t="n">
-        <v>451.5</v>
+        <v>481.75</v>
       </c>
       <c r="I17" t="n">
         <v>456.7600139004485</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
-        <v>-11.22</v>
+        <v>-18.67</v>
       </c>
       <c r="L17" t="n">
-        <v>12.82</v>
+        <v>21.39</v>
       </c>
       <c r="M17" t="n">
         <v>0.51</v>
       </c>
       <c r="N17" t="n">
-        <v>4.71</v>
+        <v>6.7</v>
       </c>
       <c r="O17" t="n">
         <v>-3.49</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>17.7</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45219</v>
+        <v>45222</v>
       </c>
       <c r="H18" t="n">
-        <v>724.35</v>
+        <v>700.4</v>
       </c>
       <c r="I18" t="n">
         <v>718.9654938058818</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="K18" t="n">
-        <v>50.36</v>
+        <v>45.39</v>
       </c>
       <c r="L18" t="n">
         <v>6.57</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>173</v>
+        <v>174</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>9</v>
+      </c>
+      <c r="U18" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>9.85</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45243</v>
+        <v>45245</v>
       </c>
       <c r="H19" t="n">
-        <v>749.9</v>
+        <v>764.65</v>
       </c>
       <c r="I19" t="n">
         <v>754.7966311068858</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K19" t="n">
-        <v>-7.07</v>
+        <v>-9.17</v>
       </c>
       <c r="L19" t="n">
-        <v>8.1</v>
+        <v>9.94</v>
       </c>
       <c r="M19" t="n">
         <v>1.84</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>10.29</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45279</v>
+        <v>45280</v>
       </c>
       <c r="H20" t="n">
-        <v>799.85</v>
+        <v>756.6</v>
       </c>
       <c r="I20" t="n">
         <v>759.5606479462791</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K20" t="n">
-        <v>4.6</v>
+        <v>-1.05</v>
       </c>
       <c r="L20" t="n">
-        <v>1.92</v>
+        <v>3.81</v>
       </c>
       <c r="M20" t="n">
         <v>1.37</v>
       </c>
       <c r="N20" t="n">
-        <v>2.45</v>
+        <v>5.41</v>
       </c>
       <c r="O20" t="n">
         <v>1.97</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>17.34</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45306</v>
+        <v>45307</v>
       </c>
       <c r="H21" t="n">
-        <v>863.9</v>
+        <v>881.85</v>
       </c>
       <c r="I21" t="n">
         <v>868.6223282919566</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K21" t="n">
-        <v>-14.18</v>
+        <v>-16.55</v>
       </c>
       <c r="L21" t="n">
-        <v>14.57</v>
+        <v>18.01</v>
       </c>
       <c r="M21" t="n">
         <v>1.13</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>9.9</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="H22" t="n">
-        <v>1722.05</v>
+        <v>1685.9</v>
       </c>
       <c r="I22" t="n">
         <v>1691.838296776792</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K22" t="n">
-        <v>95.28</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="L22" t="n">
         <v>4.52</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>173</v>
+        <v>174</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>9</v>
+      </c>
+      <c r="U22" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>15.18</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45621</v>
+        <v>45622</v>
       </c>
       <c r="H23" t="n">
-        <v>1806.3</v>
+        <v>1850.8</v>
       </c>
       <c r="I23" t="n">
         <v>1846.607631626442</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K23" t="n">
-        <v>-7.14</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>7.89</v>
+        <v>10.62</v>
       </c>
       <c r="M23" t="n">
         <v>3.23</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>14.68</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="H24" t="n">
-        <v>2002.85</v>
+        <v>1919.55</v>
       </c>
       <c r="I24" t="n">
         <v>1968.457751405045</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K24" t="n">
-        <v>8.220000000000001</v>
+        <v>3.71</v>
       </c>
       <c r="L24" t="n">
         <v>3.61</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>15.82</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45736</v>
+        <v>45737</v>
       </c>
       <c r="H25" t="n">
-        <v>1559.2</v>
+        <v>1603</v>
       </c>
       <c r="I25" t="n">
         <v>1568.713915211392</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K25" t="n">
-        <v>18.77</v>
+        <v>16.49</v>
       </c>
       <c r="L25" t="n">
         <v>4.05</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>16.78</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45874</v>
+        <v>45875</v>
       </c>
       <c r="H26" t="n">
-        <v>1748</v>
+        <v>1735.5</v>
       </c>
       <c r="I26" t="n">
         <v>1747.562525202417</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K26" t="n">
-        <v>9.050000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="L26" t="n">
         <v>13.79</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45887</v>
+        <v>45888</v>
       </c>
       <c r="H27" t="n">
-        <v>1866.6</v>
+        <v>1913.9</v>
       </c>
       <c r="I27" t="n">
         <v>1906.723323030868</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.55</v>
+        <v>-10.28</v>
       </c>
       <c r="L27" t="n">
         <v>11.26</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>10.39</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="H28" t="n">
-        <v>1801.6</v>
+        <v>1735.2</v>
       </c>
       <c r="I28" t="n">
         <v>1753.211724857198</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K28" t="n">
-        <v>-5.87</v>
+        <v>-9.34</v>
       </c>
       <c r="L28" t="n">
-        <v>8.09</v>
+        <v>12.16</v>
       </c>
       <c r="M28" t="n">
         <v>0.6</v>
       </c>
       <c r="N28" t="n">
-        <v>3.51</v>
+        <v>3.69</v>
       </c>
       <c r="O28" t="n">
         <v>2.53</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>9.75</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="H29" t="n">
-        <v>1723.4</v>
+        <v>1844.5</v>
       </c>
       <c r="I29" t="n">
         <v>1782.49491421158</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K29" t="n">
-        <v>0.68</v>
+        <v>-6.3</v>
       </c>
       <c r="L29" t="n">
-        <v>4.02</v>
+        <v>6.67</v>
       </c>
       <c r="M29" t="n">
-        <v>1.14</v>
+        <v>4.5</v>
       </c>
       <c r="N29" t="n">
-        <v>3.78</v>
+        <v>7.03</v>
       </c>
       <c r="O29" t="n">
         <v>-3.69</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>11.68</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="H30" t="n">
-        <v>1820.5</v>
+        <v>1765</v>
       </c>
       <c r="I30" t="n">
         <v>1783.552430706602</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.3</v>
+        <v>-4.31</v>
       </c>
       <c r="L30" t="n">
         <v>7.02</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>11.52</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="H31" t="n">
-        <v>1550.5</v>
+        <v>1600.6</v>
       </c>
       <c r="I31" t="n">
         <v>1570.038974651328</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K31" t="n">
-        <v>12.15</v>
+        <v>9.31</v>
       </c>
       <c r="L31" t="n">
         <v>9.859999999999999</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>11.35</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="H32" t="n">
-        <v>1671.4</v>
+        <v>1644.2</v>
       </c>
       <c r="I32" t="n">
         <v>1645.824384667286</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K32" t="n">
-        <v>4.42</v>
+        <v>2.72</v>
       </c>
       <c r="L32" t="n">
         <v>2.97</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>10.18</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="H33" t="n">
-        <v>1628.6</v>
+        <v>1684.2</v>
       </c>
       <c r="I33" t="n">
         <v>1678.114742670852</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K33" t="n">
-        <v>0.95</v>
+        <v>-2.43</v>
       </c>
       <c r="L33" t="n">
         <v>4.08</v>
@@ -2322,7 +2717,7 @@
         <v>1.5</v>
       </c>
       <c r="N33" t="n">
-        <v>2.9</v>
+        <v>3.41</v>
       </c>
       <c r="O33" t="n">
         <v>-1.63</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>11.04</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="H34" t="n">
-        <v>1548.2</v>
+        <v>1526.7</v>
       </c>
       <c r="I34" t="n">
         <v>1528.093378456629</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K34" t="n">
-        <v>-8.08</v>
+        <v>-9.35</v>
       </c>
       <c r="L34" t="n">
-        <v>9.039999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="M34" t="n">
         <v>3.69</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>9.640000000000001</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="H35" t="n">
-        <v>1630</v>
+        <v>1733</v>
       </c>
       <c r="I35" t="n">
         <v>1661.514089327552</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>-6.77</v>
+        <v>-13.51</v>
       </c>
       <c r="L35" t="n">
-        <v>9.640000000000001</v>
+        <v>14.43</v>
       </c>
       <c r="M35" t="n">
         <v>2.78</v>
       </c>
       <c r="N35" t="n">
-        <v>3.03</v>
+        <v>6.32</v>
       </c>
       <c r="O35" t="n">
         <v>-1.39</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>12.4</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="H36" t="n">
-        <v>1886.3</v>
+        <v>1207.2</v>
       </c>
       <c r="I36" t="n">
         <v>1704.066084249566</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K36" t="n">
-        <v>8.85</v>
+        <v>-30.34</v>
       </c>
       <c r="L36" t="n">
-        <v>6.64</v>
+        <v>30.34</v>
       </c>
       <c r="M36" t="n">
-        <v>1.6</v>
+        <v>10</v>
       </c>
       <c r="N36" t="n">
-        <v>3.41</v>
+        <v>36</v>
       </c>
       <c r="O36" t="n">
         <v>6.32</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2553,6 +2996,14 @@
       <c r="Q37" t="n">
         <v>23</v>
       </c>
+      <c r="R37" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4723,7 +5174,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48.9</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="6">
@@ -4733,7 +5184,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -4743,7 +5194,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8">
@@ -4753,7 +5204,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -4763,7 +5214,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -4773,7 +5224,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11">
@@ -4783,7 +5234,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -4793,7 +5244,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -4803,7 +5254,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>51.4</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="14">
@@ -4813,7 +5264,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="15">
@@ -4823,7 +5274,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.78</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="16">
@@ -4833,7 +5284,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.1</v>
+        <v>-6.52</v>
       </c>
     </row>
     <row r="17">
@@ -4843,7 +5294,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>95.28</v>
+        <v>91.18000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -4853,7 +5304,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>40</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="19">
@@ -4863,7 +5314,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9.449999999999999</v>
+        <v>12.36</v>
       </c>
     </row>
     <row r="20">
@@ -4873,7 +5324,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.92</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="21">
@@ -4883,7 +5334,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>27.2</v>
+        <v>30.34</v>
       </c>
     </row>
     <row r="22">
@@ -4893,7 +5344,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
@@ -4903,7 +5354,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -4913,7 +5364,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="25">
@@ -4923,7 +5374,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8.130000000000001</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -4933,7 +5384,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6.21</v>
+        <v>8.02</v>
       </c>
     </row>
     <row r="27">
@@ -4943,7 +5394,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>17.39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28">
@@ -4953,7 +5404,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
